--- a/temp/espc-2/searchByMAC-3.xlsx
+++ b/temp/espc-2/searchByMAC-3.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="717" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="720" uniqueCount="41">
   <si>
     <t>ЭСПЦ-2</t>
   </si>
@@ -134,6 +134,9 @@
   </si>
   <si>
     <t>17.48</t>
+  </si>
+  <si>
+    <t>1</t>
   </si>
 </sst>
 </file>
@@ -490,7 +493,7 @@
     <col min="1" max="44" width="5.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -510,25 +513,40 @@
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
+      <c r="F2" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="1"/>
+      <c r="N2" s="1" t="s">
+        <v>12</v>
+      </c>
       <c r="O2" s="1"/>
       <c r="P2" s="1"/>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R2">
+        <v>7</v>
+      </c>
+      <c r="V2">
+        <v>8</v>
+      </c>
+      <c r="Z2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="1" t="s">
         <v>1</v>
@@ -548,7 +566,7 @@
       <c r="O3" s="1"/>
       <c r="P3" s="1"/>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1" t="s">
@@ -570,7 +588,7 @@
       <c r="O4" s="1"/>
       <c r="P4" s="1"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1" t="s">
@@ -592,7 +610,7 @@
       <c r="O5" s="1"/>
       <c r="P5" s="1"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1" t="s">
@@ -614,7 +632,7 @@
       <c r="O6" s="1"/>
       <c r="P6" s="1"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1" t="s">
@@ -636,7 +654,7 @@
       <c r="O7" s="1"/>
       <c r="P7" s="1"/>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1" t="s">
@@ -658,7 +676,7 @@
       <c r="O8" s="1"/>
       <c r="P8" s="1"/>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1" t="s">
@@ -680,7 +698,7 @@
       <c r="O9" s="1"/>
       <c r="P9" s="1"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1" t="s">
@@ -702,7 +720,7 @@
       <c r="O10" s="1"/>
       <c r="P10" s="1"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1" t="s">
@@ -724,7 +742,7 @@
       <c r="O11" s="1"/>
       <c r="P11" s="1"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1" t="s">
@@ -746,7 +764,7 @@
       <c r="O12" s="1"/>
       <c r="P12" s="1"/>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1" t="s">
@@ -768,7 +786,7 @@
       <c r="O13" s="1"/>
       <c r="P13" s="1"/>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1" t="s">
@@ -790,7 +808,7 @@
       <c r="O14" s="1"/>
       <c r="P14" s="1"/>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1" t="s">
@@ -812,7 +830,7 @@
       <c r="O15" s="1"/>
       <c r="P15" s="1"/>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1" t="s">

--- a/temp/espc-2/searchByMAC-3.xlsx
+++ b/temp/espc-2/searchByMAC-3.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="720" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="937" uniqueCount="47">
   <si>
     <t>ЭСПЦ-2</t>
   </si>
@@ -137,6 +137,24 @@
   </si>
   <si>
     <t>1</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>6.2.17</t>
+  </si>
+  <si>
+    <t>6.2.16</t>
+  </si>
+  <si>
+    <t>6.2.23</t>
+  </si>
+  <si>
+    <t>6.2.22</t>
+  </si>
+  <si>
+    <t>3</t>
   </si>
 </sst>
 </file>
@@ -487,13 +505,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AB211"/>
+  <dimension ref="A1:AD211"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="44" width="5.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -513,7 +531,7 @@
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -546,7 +564,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="1" t="s">
         <v>1</v>
@@ -566,7 +584,7 @@
       <c r="O3" s="1"/>
       <c r="P3" s="1"/>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1" t="s">
@@ -584,11 +602,14 @@
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="1"/>
-      <c r="O4" s="1"/>
-      <c r="P4" s="1"/>
-    </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="N4">
+        <v>9</v>
+      </c>
+      <c r="W4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1" t="s">
@@ -606,11 +627,22 @@
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="1"/>
-      <c r="O5" s="1"/>
-      <c r="P5" s="1"/>
-    </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="O5" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="P5" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q5" s="1"/>
+      <c r="X5" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y5" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z5" s="1"/>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1" t="s">
@@ -628,11 +660,22 @@
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
-      <c r="N6" s="1"/>
-      <c r="O6" s="1"/>
-      <c r="P6" s="1"/>
-    </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="O6" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q6" s="1"/>
+      <c r="X6" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y6" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z6" s="1"/>
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1" t="s">
@@ -650,11 +693,22 @@
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
-      <c r="N7" s="1"/>
-      <c r="O7" s="1"/>
-      <c r="P7" s="1"/>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="O7" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q7" s="1"/>
+      <c r="X7" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y7" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z7" s="1"/>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1" t="s">
@@ -672,11 +726,22 @@
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
-      <c r="N8" s="1"/>
-      <c r="O8" s="1"/>
-      <c r="P8" s="1"/>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="O8" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q8" s="1"/>
+      <c r="X8" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y8" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z8" s="1"/>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1" t="s">
@@ -694,11 +759,22 @@
       <c r="K9" s="2"/>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
-      <c r="N9" s="1"/>
-      <c r="O9" s="1"/>
-      <c r="P9" s="1"/>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="O9" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P9" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q9" s="1"/>
+      <c r="X9" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y9" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z9" s="1"/>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1" t="s">
@@ -716,11 +792,32 @@
       <c r="K10" s="2"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
-      <c r="N10" s="1"/>
-      <c r="O10" s="1"/>
-      <c r="P10" s="1"/>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="N10">
+        <v>11</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q10" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="W10">
+        <v>11</v>
+      </c>
+      <c r="X10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y10" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z10" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1" t="s">
@@ -738,11 +835,26 @@
       <c r="K11" s="2"/>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
-      <c r="N11" s="1"/>
-      <c r="O11" s="1"/>
-      <c r="P11" s="1"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="O11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="P11" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="X11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y11" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z11" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1" t="s">
@@ -760,11 +872,38 @@
       <c r="K12" s="2"/>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
-      <c r="N12" s="1"/>
-      <c r="O12" s="1"/>
-      <c r="P12" s="1"/>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="N12">
+        <v>1</v>
+      </c>
+      <c r="O12" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="P12" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q12" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="R12" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="W12">
+        <v>1</v>
+      </c>
+      <c r="X12" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y12" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z12" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="AA12" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1" t="s">
@@ -782,11 +921,38 @@
       <c r="K13" s="2"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
-      <c r="N13" s="1"/>
-      <c r="O13" s="1"/>
-      <c r="P13" s="1"/>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="N13">
+        <v>1</v>
+      </c>
+      <c r="O13" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P13" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="R13" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="W13">
+        <v>1</v>
+      </c>
+      <c r="X13" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y13" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="AA13" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1" t="s">
@@ -804,11 +970,32 @@
       <c r="K14" s="2"/>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
-      <c r="N14" s="1"/>
-      <c r="O14" s="1"/>
-      <c r="P14" s="1"/>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="O14" s="1">
+        <v>6</v>
+      </c>
+      <c r="P14" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q14" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="X14" s="1">
+        <v>6</v>
+      </c>
+      <c r="Y14" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z14" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AA14" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1" t="s">
@@ -826,11 +1013,26 @@
       <c r="K15" s="2"/>
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
-      <c r="N15" s="1"/>
-      <c r="O15" s="1"/>
-      <c r="P15" s="1"/>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="P15" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R15" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y15" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AA15" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1" t="s">
@@ -848,11 +1050,26 @@
       <c r="K16" s="2"/>
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
-      <c r="N16" s="1"/>
-      <c r="O16" s="1"/>
-      <c r="P16" s="1"/>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P16" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R16" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y16" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AA16" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -866,11 +1083,38 @@
       <c r="K17" s="2"/>
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
-      <c r="N17" s="1"/>
-      <c r="O17" s="1"/>
-      <c r="P17" s="1"/>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="O17" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P17" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q17" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R17" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="S17" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="X17" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="Y17" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z17" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AA17" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB17" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="B18" s="1" t="s">
         <v>8</v>
@@ -886,11 +1130,34 @@
       <c r="K18" s="2"/>
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
-      <c r="N18" s="1"/>
       <c r="O18" s="1"/>
-      <c r="P18" s="1"/>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P18" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q18" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R18" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="S18" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="X18" s="1"/>
+      <c r="Y18" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z18" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AA18" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB18" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1" t="s">
@@ -908,11 +1175,44 @@
       <c r="K19" s="2"/>
       <c r="L19" s="1"/>
       <c r="M19" s="1"/>
-      <c r="N19" s="1"/>
-      <c r="O19" s="1"/>
-      <c r="P19" s="1"/>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="O19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="P19" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q19" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R19" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="S19" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="T19" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="X19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="Y19" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z19" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AA19" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB19" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AC19" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1" t="s">
@@ -930,11 +1230,40 @@
       <c r="K20" s="2"/>
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
-      <c r="N20" s="1"/>
       <c r="O20" s="1"/>
-      <c r="P20" s="1"/>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P20" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q20" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R20" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="S20" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="T20" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="X20" s="1"/>
+      <c r="Y20" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z20" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AA20" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB20" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AC20" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="21" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1" t="s">
@@ -952,11 +1281,56 @@
       <c r="K21" s="2"/>
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
-      <c r="N21" s="1"/>
-      <c r="O21" s="1"/>
-      <c r="P21" s="1"/>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N21">
+        <v>1</v>
+      </c>
+      <c r="O21" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="P21" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q21" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R21" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="S21" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="T21" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="U21" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="W21">
+        <v>1</v>
+      </c>
+      <c r="X21" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y21" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z21" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AA21" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB21" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AC21" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD21" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="22" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1" t="s">
@@ -974,11 +1348,51 @@
       <c r="K22" s="2"/>
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
-      <c r="N22" s="1"/>
       <c r="O22" s="1"/>
-      <c r="P22" s="1"/>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P22" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q22" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R22" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="S22" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="T22" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="U22" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="W22">
+        <v>1</v>
+      </c>
+      <c r="X22" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="Y22" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z22" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AA22" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB22" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AC22" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD22" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="23" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1" t="s">
@@ -996,11 +1410,8 @@
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
       <c r="M23" s="1"/>
-      <c r="N23" s="1"/>
-      <c r="O23" s="1"/>
-      <c r="P23" s="1"/>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1" t="s">
@@ -1018,11 +1429,14 @@
       <c r="K24" s="1"/>
       <c r="L24" s="1"/>
       <c r="M24" s="1"/>
-      <c r="N24" s="1"/>
-      <c r="O24" s="1"/>
-      <c r="P24" s="1"/>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N24">
+        <v>9</v>
+      </c>
+      <c r="W24">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1" t="s">
@@ -1040,11 +1454,22 @@
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
       <c r="M25" s="1"/>
-      <c r="N25" s="1"/>
-      <c r="O25" s="1"/>
-      <c r="P25" s="1"/>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="O25" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="P25" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q25" s="1"/>
+      <c r="X25" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y25" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z25" s="1"/>
+    </row>
+    <row r="26" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1" t="s">
@@ -1062,11 +1487,22 @@
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
-      <c r="N26" s="1"/>
-      <c r="O26" s="1"/>
-      <c r="P26" s="1"/>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="O26" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="P26" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q26" s="1"/>
+      <c r="X26" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y26" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z26" s="1"/>
+    </row>
+    <row r="27" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1" t="s">
@@ -1084,11 +1520,22 @@
       <c r="K27" s="1"/>
       <c r="L27" s="1"/>
       <c r="M27" s="1"/>
-      <c r="N27" s="1"/>
-      <c r="O27" s="1"/>
-      <c r="P27" s="1"/>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="O27" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="P27" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q27" s="1"/>
+      <c r="X27" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y27" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z27" s="1"/>
+    </row>
+    <row r="28" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1" t="s">
@@ -1106,11 +1553,22 @@
       <c r="K28" s="1"/>
       <c r="L28" s="1"/>
       <c r="M28" s="1"/>
-      <c r="N28" s="1"/>
-      <c r="O28" s="1"/>
-      <c r="P28" s="1"/>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="O28" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="P28" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q28" s="1"/>
+      <c r="X28" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y28" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z28" s="1"/>
+    </row>
+    <row r="29" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1" t="s">
@@ -1128,11 +1586,22 @@
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
       <c r="M29" s="1"/>
-      <c r="N29" s="1"/>
-      <c r="O29" s="1"/>
-      <c r="P29" s="1"/>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="O29" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P29" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q29" s="1"/>
+      <c r="X29" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y29" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z29" s="1"/>
+    </row>
+    <row r="30" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1" t="s">
@@ -1150,11 +1619,14 @@
       <c r="K30" s="1"/>
       <c r="L30" s="1"/>
       <c r="M30" s="1"/>
-      <c r="N30" s="1"/>
       <c r="O30" s="1"/>
       <c r="P30" s="1"/>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q30" s="1"/>
+      <c r="X30" s="1"/>
+      <c r="Y30" s="1"/>
+      <c r="Z30" s="1"/>
+    </row>
+    <row r="31" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1" t="s">
@@ -1172,11 +1644,26 @@
       <c r="K31" s="1"/>
       <c r="L31" s="1"/>
       <c r="M31" s="1"/>
-      <c r="N31" s="1"/>
-      <c r="O31" s="1"/>
-      <c r="P31" s="1"/>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="O31" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="P31" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q31" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="X31" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y31" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z31" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="32" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -1190,11 +1677,32 @@
       <c r="K32" s="1"/>
       <c r="L32" s="1"/>
       <c r="M32" s="1"/>
-      <c r="N32" s="1"/>
-      <c r="O32" s="1"/>
-      <c r="P32" s="1"/>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="O32" s="1">
+        <v>6</v>
+      </c>
+      <c r="P32" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q32" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R32" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="X32" s="1">
+        <v>6</v>
+      </c>
+      <c r="Y32" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z32" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AA32" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="33" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
       <c r="B33" s="1" t="s">
         <v>17</v>
@@ -1214,11 +1722,26 @@
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
       <c r="M33" s="1"/>
-      <c r="N33" s="1"/>
-      <c r="O33" s="1"/>
-      <c r="P33" s="1"/>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P33" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q33" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R33" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y33" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z33" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AA33" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="34" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1" t="s">
@@ -1244,11 +1767,26 @@
         <v>19</v>
       </c>
       <c r="M34" s="1"/>
-      <c r="N34" s="1"/>
-      <c r="O34" s="1"/>
-      <c r="P34" s="1"/>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P34" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q34" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R34" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y34" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z34" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AA34" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="35" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1" t="s">
@@ -1274,11 +1812,38 @@
         <v>19</v>
       </c>
       <c r="M35" s="1"/>
-      <c r="N35" s="1"/>
-      <c r="O35" s="1"/>
-      <c r="P35" s="1"/>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="O35" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P35" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q35" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R35" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="S35" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="X35" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="Y35" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z35" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AA35" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB35" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="36" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1" t="s">
@@ -1304,11 +1869,34 @@
         <v>19</v>
       </c>
       <c r="M36" s="1"/>
-      <c r="N36" s="1"/>
       <c r="O36" s="1"/>
-      <c r="P36" s="1"/>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P36" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q36" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R36" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="S36" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="X36" s="1"/>
+      <c r="Y36" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z36" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AA36" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB36" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="37" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1" t="s">
@@ -1326,11 +1914,32 @@
       <c r="K37" s="1"/>
       <c r="L37" s="1"/>
       <c r="M37" s="1"/>
-      <c r="N37" s="1"/>
-      <c r="O37" s="1"/>
-      <c r="P37" s="1"/>
-    </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="O37" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="P37" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q37" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R37" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="S37" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="T37" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="X37" s="1"/>
+      <c r="Y37" s="1"/>
+      <c r="Z37" s="1"/>
+      <c r="AA37" s="1"/>
+      <c r="AB37" s="1"/>
+      <c r="AC37" s="1"/>
+    </row>
+    <row r="38" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1" t="s">
@@ -1352,11 +1961,40 @@
       <c r="K38" s="1"/>
       <c r="L38" s="1"/>
       <c r="M38" s="1"/>
-      <c r="N38" s="1"/>
-      <c r="O38" s="2"/>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="O38" s="1"/>
+      <c r="P38" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q38" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R38" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="S38" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="T38" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="X38" s="1"/>
+      <c r="Y38" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z38" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AA38" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB38" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AC38" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="39" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1" t="s">
@@ -1382,11 +2020,22 @@
         <v>19</v>
       </c>
       <c r="M39" s="1"/>
-      <c r="N39" s="1"/>
       <c r="O39" s="1"/>
       <c r="P39" s="1"/>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q39" s="1"/>
+      <c r="R39" s="1"/>
+      <c r="S39" s="1"/>
+      <c r="T39" s="1"/>
+      <c r="U39" s="1"/>
+      <c r="X39" s="1"/>
+      <c r="Y39" s="1"/>
+      <c r="Z39" s="1"/>
+      <c r="AA39" s="1"/>
+      <c r="AB39" s="1"/>
+      <c r="AC39" s="1"/>
+      <c r="AD39" s="1"/>
+    </row>
+    <row r="40" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1" t="s">
@@ -1404,11 +2053,34 @@
       <c r="K40" s="1"/>
       <c r="L40" s="1"/>
       <c r="M40" s="1"/>
-      <c r="N40" s="1"/>
       <c r="O40" s="1"/>
-      <c r="P40" s="1"/>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P40" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q40" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R40" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="S40" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="T40" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="U40" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="X40" s="1"/>
+      <c r="Y40" s="1"/>
+      <c r="Z40" s="1"/>
+      <c r="AA40" s="1"/>
+      <c r="AB40" s="1"/>
+      <c r="AC40" s="1"/>
+      <c r="AD40" s="1"/>
+    </row>
+    <row r="41" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1" t="s">
@@ -1430,7 +2102,7 @@
       <c r="O41" s="1"/>
       <c r="P41" s="1"/>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1" t="s">
@@ -1460,7 +2132,7 @@
       <c r="O42" s="1"/>
       <c r="P42" s="1"/>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1" t="s">
@@ -1486,7 +2158,7 @@
       <c r="O43" s="1"/>
       <c r="P43" s="1"/>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1" t="s">
@@ -1508,7 +2180,7 @@
       <c r="O44" s="1"/>
       <c r="P44" s="1"/>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1" t="s">
@@ -1530,7 +2202,7 @@
       <c r="O45" s="1"/>
       <c r="P45" s="1"/>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1" t="s">
@@ -1560,7 +2232,7 @@
       <c r="O46" s="1"/>
       <c r="P46" s="1"/>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
@@ -1578,7 +2250,7 @@
       <c r="O47" s="1"/>
       <c r="P47" s="1"/>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A48" s="1"/>
       <c r="B48" s="1" t="s">
         <v>16</v>

--- a/temp/espc-2/searchByMAC-3.xlsx
+++ b/temp/espc-2/searchByMAC-3.xlsx
@@ -1193,6 +1193,9 @@
       <c r="T19" s="1" t="s">
         <v>27</v>
       </c>
+      <c r="W19">
+        <v>11</v>
+      </c>
       <c r="X19" s="1" t="s">
         <v>7</v>
       </c>
